--- a/docs/results/ch3_fw1_pvclust_cluster_results.xlsx
+++ b/docs/results/ch3_fw1_pvclust_cluster_results.xlsx
@@ -475,10 +475,10 @@
         <v>46</v>
       </c>
       <c r="C2" t="n">
-        <v>0.926619887160312</v>
+        <v>0.921876503229069</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0550322653400696</v>
+        <v>0.0516179629871452</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -504,10 +504,10 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>0.940189907583622</v>
+        <v>0.936873768296455</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0503469749113867</v>
+        <v>0.045328654806071</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>

--- a/docs/results/ch3_fw1_pvclust_cluster_results.xlsx
+++ b/docs/results/ch3_fw1_pvclust_cluster_results.xlsx
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>0.921876503229069</v>
+        <v>0.939216862289887</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0516179629871452</v>
+        <v>0.023687026130751</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DR-03, DR-144, DR-145, DR-156, DR-159, DR-37, LSC-07, LSC-09, LSC-12, LSC-14, LSC-15, LSC-16, LSC-17, LSC-18, LSC-19, LSC-22, LSC-24, LSC-25, LSC-26, LSC-27, LSC-29, LSC-30, LSC-31, LSC-32, LSC-37, LSC-38, LSC-39, LSC-41, LSC-45, LSC-53, LSC-55, LSC-56, LSC-57, LSC-58, LSC-60, LSC-62, SCR-01, SCR-04, SCR-06, SCR-08, SCR-09, SCR-10, SCR-11, SCR-14, SCR-18, SCR-20</t>
+          <t>DR-03, DR-144, DR-145, DR-156, DR-157, DR-159, DR-37, DR-65, LSC-07, LSC-12, LSC-14, LSC-15, LSC-16, LSC-17, LSC-18, LSC-19, LSC-22, LSC-24, LSC-25, LSC-26, LSC-27, LSC-28, LSC-29, LSC-30, LSC-31, LSC-37, LSC-38, LSC-39, LSC-41, LSC-45, LSC-47, LSC-53, LSC-55, LSC-56, LSC-57, LSC-58, LSC-60, LSC-62, SCR-01, SCR-04, SCR-06, SCR-08, SCR-09, SCR-10, SCR-11, SCR-14, SCR-18, SCR-20</t>
         </is>
       </c>
     </row>
@@ -501,13 +501,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>0.936873768296455</v>
+        <v>0.943058299283051</v>
       </c>
       <c r="D3" t="n">
-        <v>0.045328654806071</v>
+        <v>0.0259693878697327</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -519,7 +519,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DR-103, DR-109, DR-141, DR-143, DR-25, LSC-23, LSC-40, LSC-42, LSC-43, LSC-46, LSC-47, LSC-48, LSC-59, SCR-02, SCR-17, SCR-19</t>
+          <t>DR-103, DR-109, DR-141, DR-143, DR-25, LSC-23, LSC-40, LSC-42, LSC-43, LSC-46, LSC-59, SCR-02, SCR-17, SCR-19</t>
         </is>
       </c>
     </row>

--- a/docs/results/ch3_fw1_pvclust_cluster_results.xlsx
+++ b/docs/results/ch3_fw1_pvclust_cluster_results.xlsx
@@ -475,10 +475,10 @@
         <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>0.939216862289887</v>
+        <v>0.910314203026239</v>
       </c>
       <c r="D2" t="n">
-        <v>0.023687026130751</v>
+        <v>0.0245973297669218</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -504,10 +504,10 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>0.943058299283051</v>
+        <v>0.916761594606784</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0259693878697327</v>
+        <v>0.0279135878938601</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
